--- a/artfynd/A 3140-2023 artfynd.xlsx
+++ b/artfynd/A 3140-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3140-2023 artfynd.xlsx
+++ b/artfynd/A 3140-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106466552</v>
+        <v>106466554</v>
       </c>
       <c r="B2" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542173.2227144482</v>
+        <v>542178</v>
       </c>
       <c r="R2" t="n">
-        <v>7201113.407194268</v>
+        <v>7201013</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106466556</v>
+        <v>106466535</v>
       </c>
       <c r="B3" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542178.4686427886</v>
+        <v>542273</v>
       </c>
       <c r="R3" t="n">
-        <v>7201012.510648956</v>
+        <v>7201244</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,55 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106466543</v>
+        <v>106466527</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542250.1147863851</v>
+        <v>542207</v>
       </c>
       <c r="R4" t="n">
-        <v>7201413.142039545</v>
+        <v>7201200</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106466526</v>
+        <v>106466528</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542205.980762921</v>
+        <v>542243</v>
       </c>
       <c r="R5" t="n">
-        <v>7201199.98864699</v>
+        <v>7201211</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106466551</v>
+        <v>106466531</v>
       </c>
       <c r="B6" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542170.0646052163</v>
+        <v>542282</v>
       </c>
       <c r="R6" t="n">
-        <v>7201126.514028072</v>
+        <v>7201212</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106466558</v>
+        <v>106466536</v>
       </c>
       <c r="B7" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542152.604740454</v>
+        <v>542273</v>
       </c>
       <c r="R7" t="n">
-        <v>7200979.054028871</v>
+        <v>7201244</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106466559</v>
+        <v>106466546</v>
       </c>
       <c r="B8" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542096.3199045733</v>
+        <v>542196</v>
       </c>
       <c r="R8" t="n">
-        <v>7201024.504873822</v>
+        <v>7201388</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,32 +1424,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106466529</v>
+        <v>106466561</v>
       </c>
       <c r="B9" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1504,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542240.6047668818</v>
+        <v>542101</v>
       </c>
       <c r="R9" t="n">
-        <v>7201214.47702908</v>
+        <v>7201019</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,55 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106466544</v>
+        <v>106466563</v>
       </c>
       <c r="B10" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542199.4830197054</v>
+        <v>542012</v>
       </c>
       <c r="R10" t="n">
-        <v>7201389.520268273</v>
+        <v>7200990</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,37 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106466540</v>
+        <v>106466564</v>
       </c>
       <c r="B11" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542251.6370998187</v>
+        <v>541981</v>
       </c>
       <c r="R11" t="n">
-        <v>7201305.415643151</v>
+        <v>7200998</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,15 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106466549</v>
+        <v>106466521</v>
       </c>
       <c r="B12" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542117.3900374392</v>
+        <v>542384</v>
       </c>
       <c r="R12" t="n">
-        <v>7201247.525118278</v>
+        <v>7200986</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,15 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106466560</v>
+        <v>106466524</v>
       </c>
       <c r="B13" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542099.3344679853</v>
+        <v>542312</v>
       </c>
       <c r="R13" t="n">
-        <v>7201021.577554609</v>
+        <v>7201116</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,15 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106466548</v>
+        <v>106466539</v>
       </c>
       <c r="B14" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,43 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542112.4998925871</v>
+        <v>542250</v>
       </c>
       <c r="R14" t="n">
-        <v>7201383.627629878</v>
+        <v>7201309</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,15 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106466535</v>
+        <v>106466541</v>
       </c>
       <c r="B15" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2190,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542273.3079654473</v>
+        <v>542277</v>
       </c>
       <c r="R15" t="n">
-        <v>7201244.63480173</v>
+        <v>7201382</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,15 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106466539</v>
+        <v>106466549</v>
       </c>
       <c r="B16" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2302,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542249.4599596566</v>
+        <v>542118</v>
       </c>
       <c r="R16" t="n">
-        <v>7201309.202783673</v>
+        <v>7201248</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2337,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2347,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,15 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106466523</v>
+        <v>106466551</v>
       </c>
       <c r="B17" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2414,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542312.0769849115</v>
+        <v>542170</v>
       </c>
       <c r="R17" t="n">
-        <v>7201116.217285142</v>
+        <v>7201126</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2449,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2459,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,15 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106466530</v>
+        <v>106466552</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,39 +2398,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542280.9228361534</v>
+        <v>542173</v>
       </c>
       <c r="R18" t="n">
-        <v>7201216.743774481</v>
+        <v>7201114</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2566,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,15 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>106466562</v>
+        <v>106466556</v>
       </c>
       <c r="B19" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542015.5278021332</v>
+        <v>542178</v>
       </c>
       <c r="R19" t="n">
-        <v>7201000.458966983</v>
+        <v>7201013</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2678,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2688,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,15 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106466561</v>
+        <v>106466558</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2755,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542101.4996752184</v>
+        <v>542153</v>
       </c>
       <c r="R20" t="n">
-        <v>7201018.638276863</v>
+        <v>7200979</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2790,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,15 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106466536</v>
+        <v>106466562</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2867,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542273.3079654473</v>
+        <v>542016</v>
       </c>
       <c r="R21" t="n">
-        <v>7201244.63480173</v>
+        <v>7201000</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2902,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2912,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,15 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106466554</v>
+        <v>106466534</v>
       </c>
       <c r="B22" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2979,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542178.4686427886</v>
+        <v>542275</v>
       </c>
       <c r="R22" t="n">
-        <v>7201012.510648956</v>
+        <v>7201242</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3014,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3024,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,15 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106466531</v>
+        <v>106466560</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3067,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3091,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542281.8441143235</v>
+        <v>542099</v>
       </c>
       <c r="R23" t="n">
-        <v>7201211.666101676</v>
+        <v>7201022</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3126,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3136,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,37 +3029,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106466534</v>
+        <v>106466526</v>
       </c>
       <c r="B24" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3203,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542275.473188106</v>
+        <v>542206</v>
       </c>
       <c r="R24" t="n">
-        <v>7201241.695868435</v>
+        <v>7201200</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3238,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,32 +3136,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>106466527</v>
+        <v>106466529</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3315,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542206.830073584</v>
+        <v>542241</v>
       </c>
       <c r="R25" t="n">
-        <v>7201200.000635438</v>
+        <v>7201214</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3350,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3360,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3387,15 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>106466550</v>
+        <v>106466519</v>
       </c>
       <c r="B26" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542117.4318580808</v>
+        <v>542383</v>
       </c>
       <c r="R26" t="n">
-        <v>7201244.556168815</v>
+        <v>7200982</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3462,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3472,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,15 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>106466524</v>
+        <v>106466523</v>
       </c>
       <c r="B27" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3515,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3539,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542312.0769849115</v>
+        <v>542312</v>
       </c>
       <c r="R27" t="n">
-        <v>7201116.217285142</v>
+        <v>7201116</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3574,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3584,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3611,15 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>106466547</v>
+        <v>106466550</v>
       </c>
       <c r="B28" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,43 +3468,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542196.5225921356</v>
+        <v>542117</v>
       </c>
       <c r="R28" t="n">
-        <v>7201388.630085612</v>
+        <v>7201245</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3695,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3705,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3732,50 +3564,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>106466545</v>
+        <v>106466544</v>
       </c>
       <c r="B29" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542198.603833077</v>
+        <v>542200</v>
       </c>
       <c r="R29" t="n">
-        <v>7201391.628857845</v>
+        <v>7201390</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3844,15 +3676,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>106466533</v>
+        <v>106466530</v>
       </c>
       <c r="B30" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3860,34 +3687,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542275.5031720991</v>
+        <v>542281</v>
       </c>
       <c r="R30" t="n">
-        <v>7201239.57518608</v>
+        <v>7201217</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3919,7 +3751,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3929,7 +3761,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3956,15 +3788,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>106466528</v>
+        <v>106466543</v>
       </c>
       <c r="B31" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3972,34 +3799,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542242.7759704622</v>
+        <v>542250</v>
       </c>
       <c r="R31" t="n">
-        <v>7201211.113902124</v>
+        <v>7201413</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4031,7 +3863,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4041,7 +3873,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4071,12 +3903,7 @@
         <v>106466553</v>
       </c>
       <c r="B32" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4113,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542211.0010600345</v>
+        <v>542211</v>
       </c>
       <c r="R32" t="n">
-        <v>7201054.970469072</v>
+        <v>7201055</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4185,15 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>106466522</v>
+        <v>106466547</v>
       </c>
       <c r="B33" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4201,34 +4023,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542312.8843051009</v>
+        <v>542196</v>
       </c>
       <c r="R33" t="n">
-        <v>7201119.198380824</v>
+        <v>7201388</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4260,7 +4091,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4270,7 +4101,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4297,15 +4128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>106466541</v>
+        <v>106466548</v>
       </c>
       <c r="B34" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,34 +4139,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542276.4666880739</v>
+        <v>542113</v>
       </c>
       <c r="R34" t="n">
-        <v>7201381.699614435</v>
+        <v>7201384</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4372,7 +4207,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4382,7 +4217,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4409,15 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>106466563</v>
+        <v>106466533</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4425,21 +4255,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4449,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542011.8605911852</v>
+        <v>542275</v>
       </c>
       <c r="R35" t="n">
-        <v>7200989.376816755</v>
+        <v>7201240</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4484,7 +4314,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4494,7 +4324,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4521,15 +4351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>106466546</v>
+        <v>106466545</v>
       </c>
       <c r="B36" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,21 +4362,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4561,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542196.5225921356</v>
+        <v>542198</v>
       </c>
       <c r="R36" t="n">
-        <v>7201388.630085612</v>
+        <v>7201391</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4630,6 +4455,327 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>106466559</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>542096</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7201024</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-02-05</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-02-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>106466522</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>542313</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7201119</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-02-05</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-02-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>106466540</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>542252</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7201306</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-02-05</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-02-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
